--- a/03-lbo-model/LBO_Model.xlsx
+++ b/03-lbo-model/LBO_Model.xlsx
@@ -15,11 +15,11 @@
     <sheet name="Checks" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Assumptions!$A$1:$J$51</definedName>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Checks!$A$1:$F$13</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Assumptions!$A$1:$J$57</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Checks!$A$1:$F$16</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Cover!$A$1:$G$23</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Debt Schedule'!$A$1:$G$23</definedName>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Returns!$A$1:$G$32</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Debt Schedule'!$A$1:$G$31</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Returns!$A$1:$G$46</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="152">
   <si>
     <t xml:space="preserve">LBO simplifié - cas d'école sur Fnac Darty (EPA : FNAC)</t>
   </si>
@@ -66,19 +66,19 @@
     <t xml:space="preserve">Debt Schedule</t>
   </si>
   <si>
-    <t xml:space="preserve">Cash sweep sur 5 ans : EBITDA, impôt, capex, BFR, remboursement de dette, accumulation de trésorerie</t>
+    <t xml:space="preserve">Cash sweep sur 5 ans : EBITDA, impôt, capex, BFR, cascade amortissement obligatoire puis optionnel, ratio de couverture des intérêts</t>
   </si>
   <si>
     <t xml:space="preserve">Returns</t>
   </si>
   <si>
-    <t xml:space="preserve">IRR, MOIC et pont de création de valeur (EBITDA / désendettement / frais)</t>
+    <t xml:space="preserve">IRR, MOIC, pont de création de valeur (EBITDA / désendettement / frais) et sensibilité à deux dimensions (prime d'offre x multiple de sortie)</t>
   </si>
   <si>
     <t xml:space="preserve">Checks</t>
   </si>
   <si>
-    <t xml:space="preserve">Contrôles de cohérence du modèle</t>
+    <t xml:space="preserve">Contrôles de cohérence du modèle et covenants de crédit hypothétiques (levier, couverture des intérêts)</t>
   </si>
   <si>
     <t xml:space="preserve">Sources (données réelles de départ uniquement)</t>
@@ -159,7 +159,7 @@
     <t xml:space="preserve">Dette nette FY2025 (position de trésorerie nette, réelle)</t>
   </si>
   <si>
-    <t xml:space="preserve">958 - 1 104 = -146 M€ : Fnac Darty est en position de cash net, pas de dette nette - lecture cohérente avec celle retenue dans le projet 2.</t>
+    <t xml:space="preserve">958 - 1 104 = -146 M€ : Fnac Darty est en position de cash net, pas de dette nette. Lecture cohérente avec celle retenue dans le projet 2.</t>
   </si>
   <si>
     <t xml:space="preserve">EMPLOIS (USES)</t>
@@ -258,6 +258,27 @@
     <t xml:space="preserve">Hypothèse prudente : la création de valeur vient de la croissance et du désendettement, pas d'un re-rating.</t>
   </si>
   <si>
+    <t xml:space="preserve">STRUCTURE DE REMBOURSEMENT ET COVENANTS (HYPOTHÈSES)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amortissement obligatoire dette senior (%/an)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypothèse personnelle : amortissement minimal usuel d'un prêt à terme institutionnel en LBO (Term Loan A/B), généralement compris entre 1 % et 5 % par an avant cash sweep (BIWS, LBO Model Guide, pages 9 et 44).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covenant de levier maximal (dette senior/EBITDA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypothèse personnelle de covenant de maintenance, dans la fourchette usuelle citée par le guide BIWS LBO Model (Senior Debt / EBITDA ne doit pas dépasser 2,0x, page 45).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covenant de couverture des intérêts (EBITDA/intérêts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypothèse personnelle de covenant de maintenance, dans la fourchette usuelle citée par le guide BIWS LBO Model (EBITDA / Interest Expense ne doit pas descendre sous 5,0x, page 45).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cash sweep - 5 ans</t>
   </si>
   <si>
@@ -324,6 +345,24 @@
     <t xml:space="preserve">Lecture : le FCF disponible (ligne 16) rembourse la dette senior en priorité (cash sweep à 100 %) ; une fois la dette intégralement remboursée (ligne 18 = 0), le FCF excédentaire s'accumule en trésorerie (lignes 20-21) plutôt que de disparaître du modèle.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÉMO : CASCADE DE REMBOURSEMENT ET RATIO DE COUVERTURE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dont amortissement obligatoire (mémo, priorité de paiement)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dont remboursement optionnel, cash sweep (mémo, résiduel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecture : le remboursement total (ligne 17) suit la cascade standard d'un prêt à terme en LBO, l'amortissement obligatoire est réglé en priorité, puis l'excédent de trésorerie disponible (cash sweep) est affecté en remboursement optionnel du solde restant, conformément à la hiérarchie décrite dans le guide BIWS LBO Model (Key Rule n°3 : les remboursements obligatoires sont toujours réglés avant les remboursements optionnels).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio de couverture des intérêts (EBITDA / charge d'intérêts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecture : en Année 5, la dette senior est intégralement remboursée (charge d'intérêts nulle), le ratio affiche 0 par convention de calcul (IFERROR) plutôt qu'une erreur de division ; le contrôle de couverture des intérêts (onglet Checks) ne porte donc que sur les années où la dette senior porte encore intérêt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rendement du sponsor : IRR, MOIC, pont de création de valeur</t>
   </si>
   <si>
@@ -402,6 +441,18 @@
     <t xml:space="preserve">Lecture : l'apport en fonds propres du sponsor est faible (16,9 % du total des emplois, réf. Assumptions C42) car la trésorerie excédentaire de la cible finance une large part de la transaction. Ce levier mécanique amplifie le MOIC pour un même montant de création de valeur en euros : point de vigilance, pas une erreur de calcul (voir Checks).</t>
   </si>
   <si>
+    <t xml:space="preserve">SENSIBILITÉ DE L'IRR : PRIME D'OFFRE x MULTIPLE DE SORTIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecture : dans ce modèle, la dette senior (fixée en % de l'EBITDA d'entrée) et le calendrier de désendettement ne dépendent ni de la prime payée ni du multiple de sortie ; seuls l'apport en fonds propres à l'entrée et la valeur des fonds propres à la sortie varient avec ces deux paramètres, ce qui permet un calcul direct par formule pour chaque scénario (construction analogue aux tables de sensibilité du guide BIWS LBO Model, page 19 : prime d'offre x multiple de sortie).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime d'offre \ multiple de sortie (VE/EBITDA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La cellule encadrée (prime d'offre 20 %, multiple de sortie égal au multiple d'entrée) correspond exactement au scénario central présenté ci-dessus (IRR 37,8 %, ligne 19) : elle sert de contrôle de cohérence entre la table de sensibilité et le calcul central du modèle.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Contrôles de cohérence</t>
   </si>
   <si>
@@ -427,6 +478,12 @@
   </si>
   <si>
     <t xml:space="preserve">MOIC et IRR cohérents (MOIC &gt; 1 si IRR &gt; 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levier senior à l'entrée respecte le covenant hypothétique (dette senior / EBITDA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Couverture des intérêts respecte le covenant hypothétique chaque année (EBITDA / intérêts)</t>
   </si>
   <si>
     <t xml:space="preserve">Synthèse</t>
@@ -444,7 +501,7 @@
     <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="169" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -525,6 +582,21 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -546,7 +618,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -560,6 +632,36 @@
       <top/>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F3864"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F3864"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F3864"/>
       </bottom>
       <diagonal/>
     </border>
@@ -589,105 +691,129 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1091,7 +1217,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:J51"/>
+  <dimension ref="B2:J56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58"/>
@@ -1591,8 +1717,69 @@
       <c r="I51" s="7"/>
       <c r="J51" s="7"/>
     </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+    </row>
+    <row r="55" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+    </row>
+    <row r="56" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="E6:J6"/>
     <mergeCell ref="E8:J8"/>
@@ -1608,10 +1795,13 @@
     <mergeCell ref="E38:J38"/>
     <mergeCell ref="E40:J40"/>
     <mergeCell ref="E51:J51"/>
+    <mergeCell ref="E54:J54"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="E56:J56"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1624,7 +1814,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G23"/>
+  <dimension ref="B2:G30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58"/>
@@ -1633,7 +1823,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1647,24 +1837,24 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C5" s="20" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="9" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C6" s="16" t="n">
         <f aca="false">Assumptions!$C$13*(1+Assumptions!$C$47)</f>
@@ -1689,7 +1879,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C7" s="16" t="n">
         <f aca="false">Assumptions!$C$17*(1+Assumptions!$C$46)</f>
@@ -1714,7 +1904,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C8" s="16" t="n">
         <f aca="false">C6*Assumptions!$C$15</f>
@@ -1739,7 +1929,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="9" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C9" s="16" t="n">
         <f aca="false">C7-C8</f>
@@ -1764,7 +1954,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C10" s="16" t="n">
         <f aca="false">Assumptions!$C$39</f>
@@ -1789,7 +1979,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C11" s="16" t="n">
         <f aca="false">C10*Assumptions!$C$40</f>
@@ -1814,7 +2004,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C12" s="16" t="n">
         <f aca="false">C9-C11</f>
@@ -1839,7 +2029,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="9" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C13" s="16" t="n">
         <f aca="false">MAX(C12,0)*Assumptions!$C$50</f>
@@ -1864,7 +2054,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="9" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C14" s="16" t="n">
         <f aca="false">C6*Assumptions!$C$48</f>
@@ -1889,7 +2079,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="9" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C15" s="16" t="n">
         <f aca="false">-(C6-Assumptions!$C$13)*Assumptions!$C$49</f>
@@ -1914,7 +2104,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="8" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">C7-C13-C14+C15</f>
@@ -1939,7 +2129,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C17" s="16" t="n">
         <f aca="false">MIN(MAX(C16,0),C10)</f>
@@ -1964,7 +2154,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C18" s="16" t="n">
         <f aca="false">C10-C17</f>
@@ -1989,7 +2179,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C20" s="16" t="n">
         <f aca="false">C16-C17</f>
@@ -2014,7 +2204,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="8" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C21" s="14" t="n">
         <f aca="false">C20</f>
@@ -2039,7 +2229,7 @@
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -2047,14 +2237,122 @@
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
     </row>
+    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <f aca="false">MIN(Assumptions!$C$54*Assumptions!$C$39,C17)</f>
+        <v>9.42174</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <f aca="false">MIN(Assumptions!$C$54*Assumptions!$C$39,D17)</f>
+        <v>9.42174</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <f aca="false">MIN(Assumptions!$C$54*Assumptions!$C$39,E17)</f>
+        <v>9.42174</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <f aca="false">MIN(Assumptions!$C$54*Assumptions!$C$39,F17)</f>
+        <v>9.42174</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <f aca="false">MIN(Assumptions!$C$54*Assumptions!$C$39,G17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <f aca="false">C17-C26</f>
+        <v>251.9056375</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <f aca="false">D17-D26</f>
+        <v>256.860758115625</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <f aca="false">E17-E26</f>
+        <v>262.047832316246</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <f aca="false">F17-F26</f>
+        <v>133.672812068129</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <f aca="false">G17-G26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <f aca="false">IFERROR(C7/C11,0)</f>
+        <v>9.32126696832579</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <f aca="false">IFERROR(D7/D11,0)</f>
+        <v>13.2859923912655</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <f aca="false">IFERROR(E7/E11,0)</f>
+        <v>22.4744356530471</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <f aca="false">IFERROR(F7/F11,0)</f>
+        <v>67.0648004481371</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <f aca="false">IFERROR(G7/G11,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B30:G30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2067,7 +2365,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G32"/>
+  <dimension ref="B2:G44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58"/>
@@ -2077,7 +2375,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2091,7 +2389,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -2101,7 +2399,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="9" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C6" s="21" t="n">
         <f aca="false">'Debt Schedule'!G7</f>
@@ -2110,7 +2408,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C7" s="22" t="n">
         <f aca="false">Assumptions!C51</f>
@@ -2119,7 +2417,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="9" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C8" s="16" t="n">
         <f aca="false">C6*C7</f>
@@ -2128,7 +2426,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="9" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C9" s="21" t="n">
         <f aca="false">'Debt Schedule'!G18</f>
@@ -2137,7 +2435,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">Assumptions!C33</f>
@@ -2146,7 +2444,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">'Debt Schedule'!G21</f>
@@ -2155,7 +2453,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="8" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C12" s="14" t="n">
         <f aca="false">C8-C9+C10+C11</f>
@@ -2164,7 +2462,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -2174,7 +2472,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="9" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C15" s="21" t="n">
         <f aca="false">Assumptions!C41</f>
@@ -2183,7 +2481,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="9" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C16" s="16" t="n">
         <f aca="false">C12</f>
@@ -2192,7 +2490,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C17" s="23" t="n">
         <f aca="false">C16/C15</f>
@@ -2201,7 +2499,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>5</v>
@@ -2209,7 +2507,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C19" s="24" t="n">
         <f aca="false">C17^(1/C18)-1</f>
@@ -2218,7 +2516,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -2228,7 +2526,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C22" s="21" t="n">
         <f aca="false">Assumptions!C33</f>
@@ -2237,7 +2535,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="9" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C23" s="16" t="n">
         <f aca="false">Assumptions!C39-C22</f>
@@ -2246,7 +2544,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="9" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C24" s="16" t="n">
         <f aca="false">C9-(C10+C11)</f>
@@ -2255,7 +2553,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="9" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C25" s="16" t="n">
         <f aca="false">(C6-Assumptions!C17)*Assumptions!C37</f>
@@ -2264,7 +2562,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="9" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C26" s="16" t="n">
         <f aca="false">C6*(C7-Assumptions!C37)</f>
@@ -2273,7 +2571,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="9" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C27" s="16" t="n">
         <f aca="false">C23-C24</f>
@@ -2282,7 +2580,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="9" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="C28" s="21" t="n">
         <f aca="false">-Assumptions!C28</f>
@@ -2291,7 +2589,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="8" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C29" s="14" t="n">
         <f aca="false">SUM(C25:C28)</f>
@@ -2300,7 +2598,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="9" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C30" s="16" t="n">
         <f aca="false">C16-C15</f>
@@ -2309,7 +2607,7 @@
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="7" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -2317,14 +2615,220 @@
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
     </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="35" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" s="27" t="n">
+        <f aca="false">$C$7-0.4</f>
+        <v>1.52413409837249</v>
+      </c>
+      <c r="D37" s="27" t="n">
+        <f aca="false">$C$7-0.2</f>
+        <v>1.72413409837249</v>
+      </c>
+      <c r="E37" s="27" t="n">
+        <f aca="false">$C$7</f>
+        <v>1.92413409837249</v>
+      </c>
+      <c r="F37" s="27" t="n">
+        <f aca="false">$C$7+0.2</f>
+        <v>2.12413409837249</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <f aca="false">$C$7+0.4</f>
+        <v>2.32413409837249</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="28" t="n">
+        <f aca="false">Assumptions!$C$8-0.2</f>
+        <v>0</v>
+      </c>
+      <c r="C38" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*C$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B38)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.57013703257662</v>
+      </c>
+      <c r="D38" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*D$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B38)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.594519060334162</v>
+      </c>
+      <c r="E38" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*E$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B38)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.617494999456395</v>
+      </c>
+      <c r="F38" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*F$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B38)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.639235106781798</v>
+      </c>
+      <c r="G38" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*G$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B38)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.659879579771485</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="28" t="n">
+        <f aca="false">Assumptions!$C$8-0.1</f>
+        <v>0.1</v>
+      </c>
+      <c r="C39" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*C$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B39)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.426961013631644</v>
+      </c>
+      <c r="D39" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*D$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B39)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.449119718458956</v>
+      </c>
+      <c r="E39" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*E$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B39)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.470000551595665</v>
+      </c>
+      <c r="F39" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*F$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B39)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.489758244677147</v>
+      </c>
+      <c r="G39" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*G$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B39)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.50852021098458</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="28" t="n">
+        <f aca="false">Assumptions!$C$8</f>
+        <v>0.2</v>
+      </c>
+      <c r="C40" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*C$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B40)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.337933688586565</v>
+      </c>
+      <c r="D40" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*D$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B40)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.358709923817025</v>
+      </c>
+      <c r="E40" s="30" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*E$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B40)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.378288013079784</v>
+      </c>
+      <c r="F40" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*F$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B40)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.396813034387264</v>
+      </c>
+      <c r="G40" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*G$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B40)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.414404451775013</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="28" t="n">
+        <f aca="false">Assumptions!$C$8+0.1</f>
+        <v>0.3</v>
+      </c>
+      <c r="C41" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*C$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B41)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.274403355534693</v>
+      </c>
+      <c r="D41" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*D$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B41)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.294193053722985</v>
+      </c>
+      <c r="E41" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*E$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B41)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.312841498608005</v>
+      </c>
+      <c r="F41" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*F$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B41)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.330486879329784</v>
+      </c>
+      <c r="G41" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*G$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B41)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.347242987303448</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="28" t="n">
+        <f aca="false">Assumptions!$C$8+0.2</f>
+        <v>0.4</v>
+      </c>
+      <c r="C42" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*C$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B42)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.225535968178216</v>
+      </c>
+      <c r="D42" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*D$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B42)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.244566824322633</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*E$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B42)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.262500188871561</v>
+      </c>
+      <c r="F42" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*F$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B42)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.279468952060093</v>
+      </c>
+      <c r="G42" s="29" t="n">
+        <f aca="false">(('Debt Schedule'!$G$7*G$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B42)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
+        <v>0.295582541936657</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G36"/>
+    <mergeCell ref="B44:G44"/>
   </mergeCells>
+  <conditionalFormatting sqref="C38:G42">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF1F3864"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2337,7 +2841,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:F13"/>
+  <dimension ref="B2:F15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="72"/>
@@ -2347,7 +2851,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2356,15 +2860,15 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="9" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="D6" s="9" t="str">
         <f aca="false">IF(ROUND(Assumptions!C43-Assumptions!C29,1)=0,"OK","A VERIFIER")</f>
@@ -2373,7 +2877,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D7" s="9" t="str">
         <f aca="false">IF(ROUND(Returns!C29-Returns!C30,1)=0,"OK","A VERIFIER")</f>
@@ -2382,7 +2886,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="9" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D8" s="9" t="str">
         <f aca="false">IF(MIN('Debt Schedule'!C18:G18)&gt;=0,"OK","A VERIFIER")</f>
@@ -2391,7 +2895,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="9" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="D9" s="9" t="str">
         <f aca="false">IF(Assumptions!C41&gt;0,"OK","A VERIFIER")</f>
@@ -2400,7 +2904,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="D10" s="9" t="str">
         <f aca="false">IF(MIN('Debt Schedule'!C16:G16)&gt;=0,"OK","A VERIFIER")</f>
@@ -2409,19 +2913,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="D11" s="9" t="str">
         <f aca="false">IF(AND(Returns!C17&gt;1,Returns!C19&gt;0),"OK","A VERIFIER")</f>
         <v>OK</v>
       </c>
     </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="9" t="str">
+        <f aca="false">IF(Assumptions!$C$38&lt;=Assumptions!$C$55,"OK","A VERIFIER")</f>
+        <v>OK</v>
+      </c>
+    </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13" s="8" t="str">
-        <f aca="false">IF(COUNTIF(D6:D11,"OK")=6,"Tous les contrôles sont OK","Au moins un contrôle à vérifier")</f>
+      <c r="B13" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9" t="str">
+        <f aca="false">IF(_xlfn.MINIFS('Debt Schedule'!$C$29:$G$29,'Debt Schedule'!$C$11:$G$11,"&gt;0")&gt;=Assumptions!$C$56,"OK","A VERIFIER")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="8" t="str">
+        <f aca="false">IF(COUNTIF(D6:D13,"OK")=8,"Tous les contrôles sont OK","Au moins un contrôle à vérifier")</f>
         <v>Tous les contrôles sont OK</v>
       </c>
     </row>
@@ -2431,7 +2954,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/03-lbo-model/LBO_Model.xlsx
+++ b/03-lbo-model/LBO_Model.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Point clé : Fnac Darty est en position de cash net</t>
   </si>
   <si>
-    <t xml:space="preserve">La dette financière brute hors IFRS16 (958 M€) est inférieure à la trésorerie réelle (1 104 M€) : la cible a 146 M€ de plus de cash que de dette brute. Ce financement reprend ce point (voir projet 2 et projet 4 du portfolio) : la trésorerie excédentaire de la cible finance une partie du prix, ce qui réduit mécaniquement le besoin de dette senior externe et explique le levier modéré retenu (1,7x EBITDA d'entrée, contre un multiple usuel de 3,0x) par rapport à une cible endettée.</t>
+    <t xml:space="preserve">La dette financière brute hors IFRS16 (958 M€) est inférieure à la trésorerie réelle (1 104 M€) : la cible a 146 M€ de plus de cash que de dette brute. Cette trésorerie étant à son point haut saisonnier au 31 décembre, 8 % du CA sont conservés au bilan ; seul le solde finance une partie du prix (voir projets 2 et 4 du portfolio), ce qui réduit le besoin de dette senior externe et explique le levier modéré retenu (1,7x EBITDA d'entrée, contre un multiple usuel de 3,0x).</t>
   </si>
   <si>
     <t xml:space="preserve">Sommaire</t>
@@ -186,19 +186,19 @@
     <t xml:space="preserve">SOURCES (FINANCEMENT)</t>
   </si>
   <si>
-    <t xml:space="preserve">Trésorerie plancher conservée (% du CA, hypothèse)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypothèse personnelle : niveau de trésorerie minimum conservé pour l'exploitation de la cible, non mobilisé pour financer la transaction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trésorerie plancher conservée (M€)</t>
+    <t xml:space="preserve">Trésorerie conservée au bilan (exploitation et saisonnalité, % du CA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypothèse personnelle : trésorerie au 31/12 gonflée par la saisonnalité (BFR négatif), en partie non mobilisable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trésorerie conservée au bilan (M€)</t>
   </si>
   <si>
     <t xml:space="preserve">Trésorerie excédentaire utilisée pour financer la transaction</t>
   </si>
   <si>
-    <t xml:space="preserve">La trésorerie de la cible au-delà du plancher réduit le besoin de financement externe (dette + fonds propres).</t>
+    <t xml:space="preserve">Seule la trésorerie au-delà du besoin d'exploitation et saisonnier réduit le besoin de financement externe.</t>
   </si>
   <si>
     <t xml:space="preserve">Besoin de financement externe (dette + fonds propres)</t>
@@ -213,7 +213,7 @@
     <t xml:space="preserve">Levier senior (x EBITDA d'entrée, hypothèse)</t>
   </si>
   <si>
-    <t xml:space="preserve">Revu à la baisse par rapport à un levier usuel de 3,0x : la position de cash net de la cible finance une large part du prix et réduit le besoin de dette externe.</t>
+    <t xml:space="preserve">Revu à la baisse par rapport à un levier usuel de 3,0x : la cible part d'une position de cash net et une partie de sa trésorerie finance le prix, ce qui réduit le besoin de dette externe.</t>
   </si>
   <si>
     <t xml:space="preserve">Dette senior à l'entrée</t>
@@ -381,7 +381,7 @@
     <t xml:space="preserve">- Dette senior restante (fin Année 5)</t>
   </si>
   <si>
-    <t xml:space="preserve">+ Trésorerie plancher conservée (réf. Assumptions)</t>
+    <t xml:space="preserve">+ Trésorerie conservée au bilan (réf. Assumptions)</t>
   </si>
   <si>
     <t xml:space="preserve">+ Trésorerie excédentaire accumulée (fin Année 5)</t>
@@ -411,10 +411,10 @@
     <t xml:space="preserve">PONT DE CRÉATION DE VALEUR (fonds propres)</t>
   </si>
   <si>
-    <t xml:space="preserve">Entrée : trésorerie plancher conservée (réf. Assumptions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dette nette de la structure à l'entrée (dette senior - trésorerie plancher)</t>
+    <t xml:space="preserve">Entrée : trésorerie conservée au bilan (réf. Assumptions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dette nette de la structure à l'entrée (dette senior - trésorerie conservée)</t>
   </si>
   <si>
     <t xml:space="preserve">Dette nette de la structure à la sortie</t>
@@ -438,7 +438,7 @@
     <t xml:space="preserve">Création de valeur réelle (sortie - entrée, contrôle croisé)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture : l'apport en fonds propres du sponsor est faible (16,9 % du total des emplois, réf. Assumptions C42) car la trésorerie excédentaire de la cible finance une large part de la transaction. Ce levier mécanique amplifie le MOIC pour un même montant de création de valeur en euros : point de vigilance, pas une erreur de calcul (voir Checks).</t>
+    <t xml:space="preserve">Lecture : l'apport en fonds propres du sponsor représente 44,9 % du total des emplois (51,3 % du besoin de financement externe, réf. Assumptions C42), un niveau cohérent avec les structures LBO actuelles. Le rendement repose sur le désendettement et l'accumulation de trésorerie, sans aucune expansion de multiple.</t>
   </si>
   <si>
     <t xml:space="preserve">SENSIBILITÉ DE L'IRR : PRIME D'OFFRE x MULTIPLE DE SORTIE</t>
@@ -450,7 +450,7 @@
     <t xml:space="preserve">Prime d'offre \ multiple de sortie (VE/EBITDA)</t>
   </si>
   <si>
-    <t xml:space="preserve">La cellule encadrée (prime d'offre 20 %, multiple de sortie égal au multiple d'entrée) correspond exactement au scénario central présenté ci-dessus (IRR 37,8 %, ligne 19) : elle sert de contrôle de cohérence entre la table de sensibilité et le calcul central du modèle.</t>
+    <t xml:space="preserve">La cellule encadrée (prime d'offre 20 %, multiple de sortie égal au multiple d'entrée) correspond exactement au scénario central présenté ci-dessus (IRR 20,1 %, ligne 19) : elle sert de contrôle de cohérence entre la table de sensibilité et le calcul central du modèle.</t>
   </si>
   <si>
     <t xml:space="preserve">Contrôles de cohérence</t>
@@ -696,123 +696,123 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1518,7 +1518,7 @@
         <v>51</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>52</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C33" s="16" t="n">
         <f aca="false">C13*C32</f>
-        <v>206.6</v>
+        <v>826.4</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C34" s="16" t="n">
         <f aca="false">C21-C33</f>
-        <v>897.4</v>
+        <v>277.6</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>55</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C35" s="14" t="n">
         <f aca="false">C29-C34</f>
-        <v>1316.401472</v>
+        <v>1936.201472</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C41" s="14" t="n">
         <f aca="false">C35-C39</f>
-        <v>374.227472</v>
+        <v>994.027472</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C42" s="19" t="n">
         <f aca="false">C41/C35</f>
-        <v>0.284280654465874</v>
+        <v>0.513390515591964</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">Assumptions!C33</f>
-        <v>206.6</v>
+        <v>826.4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C12" s="14" t="n">
         <f aca="false">C8-C9+C10+C11</f>
-        <v>1861.38222119012</v>
+        <v>2481.18222119012</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C15" s="21" t="n">
         <f aca="false">Assumptions!C41</f>
-        <v>374.227472</v>
+        <v>994.027472</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="C16" s="16" t="n">
         <f aca="false">C12</f>
-        <v>1861.38222119012</v>
+        <v>2481.18222119012</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="C17" s="23" t="n">
         <f aca="false">C16/C15</f>
-        <v>4.97393259570777</v>
+        <v>2.49609018973886</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="C19" s="24" t="n">
         <f aca="false">C17^(1/C18)-1</f>
-        <v>0.378288013079784</v>
+        <v>0.200748505247262</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C22" s="21" t="n">
         <f aca="false">Assumptions!C33</f>
-        <v>206.6</v>
+        <v>826.4</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="C23" s="16" t="n">
         <f aca="false">Assumptions!C39-C22</f>
-        <v>735.574</v>
+        <v>115.774</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C24" s="16" t="n">
         <f aca="false">C9-(C10+C11)</f>
-        <v>-625.139767710674</v>
+        <v>-1244.93976771067</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2675,23 +2675,23 @@
       </c>
       <c r="C38" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*C$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B38)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.57013703257662</v>
+        <v>0.230658902285587</v>
       </c>
       <c r="D38" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*D$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B38)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.594519060334162</v>
+        <v>0.244561092946846</v>
       </c>
       <c r="E38" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*E$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B38)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.617494999456395</v>
+        <v>0.257868511574317</v>
       </c>
       <c r="F38" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*F$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B38)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.639235106781798</v>
+        <v>0.270635519070148</v>
       </c>
       <c r="G38" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*G$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B38)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.659879579771485</v>
+        <v>0.282909119362724</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2701,23 +2701,23 @@
       </c>
       <c r="C39" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*C$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B39)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.426961013631644</v>
+        <v>0.200773725807596</v>
       </c>
       <c r="D39" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*D$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B39)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.449119718458956</v>
+        <v>0.214338317300986</v>
       </c>
       <c r="E39" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*E$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B39)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.470000551595665</v>
+        <v>0.227322580134914</v>
       </c>
       <c r="F39" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*F$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B39)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.489758244677147</v>
+        <v>0.239779555117756</v>
       </c>
       <c r="G39" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*G$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B39)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.50852021098458</v>
+        <v>0.25175510474001</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2727,23 +2727,23 @@
       </c>
       <c r="C40" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*C$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B40)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.337933688586565</v>
+        <v>0.174774488582425</v>
       </c>
       <c r="D40" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*D$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B40)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.358709923817025</v>
+        <v>0.188045378586084</v>
       </c>
       <c r="E40" s="30" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*E$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B40)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.378288013079784</v>
+        <v>0.200748505247262</v>
       </c>
       <c r="F40" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*F$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B40)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.396813034387264</v>
+        <v>0.212935760931016</v>
       </c>
       <c r="G40" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*G$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B40)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.414404451775013</v>
+        <v>0.224652015109975</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2753,23 +2753,23 @@
       </c>
       <c r="C41" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*C$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B41)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.274403355534693</v>
+        <v>0.151824869200883</v>
       </c>
       <c r="D41" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*D$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B41)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.294193053722985</v>
+        <v>0.164836507852561</v>
       </c>
       <c r="E41" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*E$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B41)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.312841498608005</v>
+        <v>0.177291474611848</v>
       </c>
       <c r="F41" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*F$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B41)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.330486879329784</v>
+        <v>0.189240648108795</v>
       </c>
       <c r="G41" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*G$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B41)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.347242987303448</v>
+        <v>0.200728021275613</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2779,23 +2779,23 @@
       </c>
       <c r="C42" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*C$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B42)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.225535968178216</v>
+        <v>0.13132714722794</v>
       </c>
       <c r="D42" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*D$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B42)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.244566824322633</v>
+        <v>0.144107232491055</v>
       </c>
       <c r="E42" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*E$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B42)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.262500188871561</v>
+        <v>0.156340552320639</v>
       </c>
       <c r="F42" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*F$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B42)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.279468952060093</v>
+        <v>0.168077079917418</v>
       </c>
       <c r="G42" s="29" t="n">
         <f aca="false">(('Debt Schedule'!$G$7*G$37-'Debt Schedule'!$G$18+Assumptions!$C$33+'Debt Schedule'!$G$21)/((Assumptions!$C$6*(1+$B42)*Assumptions!$C$7+Assumptions!$C$20)*(1+Assumptions!$C$27)-Assumptions!$C$34-Assumptions!$C$39))^(1/$C$18)-1</f>
-        <v>0.295582541936657</v>
+        <v>0.17936002532124</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
